--- a/order_forms/033_nails_with_liz_wish_list--order_forms.xlsx
+++ b/order_forms/033_nails_with_liz_wish_list--order_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="31" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -520,7 +520,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>color_sticky_note</t>
+          <t>color_stickynote</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -531,7 +531,7 @@
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>nail_type_id</t>
+          <t>nail_type</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -571,7 +571,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Length</t>
+          <t>What is your preferred nail length?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -594,7 +594,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Width</t>
+          <t>What is your preferred nail width?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -617,7 +617,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Shape</t>
+          <t>What shape do you like your nails to be?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -640,7 +640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>What type of nail?</t>
+          <t>What type of nail do you like?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -663,7 +663,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Length</t>
+          <t>Nail Nail Length</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -686,7 +686,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Width</t>
+          <t>Nail Nail Width</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -709,7 +709,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Shape</t>
+          <t>Nail Nail Shape</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -755,7 +755,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Length</t>
+          <t>Nail Nail Length 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,320 +768,21 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>nail_nail_width_2</t>
+          <t>nail_nail_shape_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Width</t>
+          <t>Nail Nail Shape 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>nail_nail_shape_2</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Shape</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>nail_nail_length_3</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Length</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>nail_nail_shape_3</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Shape</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>nail_nail_length_4</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Length</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>nail_nail_width_2</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Width</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>nail_special_nail_2</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Nail</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>nail_nail_shape_2</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Shape</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>nail_nail_length_5</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Length</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>nail_nail_width_3</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Width</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>nail_nail_shape_4</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Shape</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>nail_nail_length_6</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Length</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>nail_nail_width_4</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Width</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>nail_nail_shape_5</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Shape</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,7 +799,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -1126,7 +827,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>color_sticky_note_choices</t>
+          <t>color_stickynote_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1143,7 +844,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>color_sticky_note_choices</t>
+          <t>color_stickynote_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1160,7 +861,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>color_sticky_note_choices</t>
+          <t>color_stickynote_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1177,51 +878,51 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>nail_type_id_choices</t>
+          <t>nail_type_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>nail_type_id_choices</t>
+          <t>nail_type_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>nail_shape_choices</t>
+          <t>nail_type_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>oval</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Oval</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1233,12 +934,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>round</t>
+          <t>oval</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Round</t>
+          <t>Oval</t>
         </is>
       </c>
     </row>
@@ -1250,12 +951,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>square</t>
+          <t>round</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Square</t>
+          <t>Round</t>
         </is>
       </c>
     </row>
@@ -1284,12 +985,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>nail</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Nail</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1441,176 +1142,6 @@
         </is>
       </c>
       <c r="C20" t="inlineStr">
-        <is>
-          <t>Round</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>nail_nail_shape_3_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>oval</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Oval</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>nail_nail_shape_3_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>round</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Round</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>nail_nail_width_2_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>narrow</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Narrow</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>nail_nail_width_2_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>wide</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Wide</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>nail_nail_shape_2_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>oval</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Oval</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>nail_nail_shape_2_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>round</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Round</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>nail_nail_shape_4_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>oval</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Oval</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>nail_nail_shape_4_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>round</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Round</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>nail_nail_shape_5_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>oval</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Oval</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>nail_nail_shape_5_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>round</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
         <is>
           <t>Round</t>
         </is>
